--- a/wiki/reports/daily/2026-10-01_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-01_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+#,##0;-#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,13 +75,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +91,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,34 +173,25 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,6 +199,30 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-01 07:59   |   전일: 없음   |   월평균 기준: 이전 작업일 0일 평균   |   10월 누적 작업일: 0일</t>
+          <t>생성: 2026-10-01 16:00   |   전일: 없음   |   월평균 기준: 이전 작업일 0일 평균   |   10월 누적 작업일: 1일</t>
         </is>
       </c>
     </row>
@@ -660,7 +675,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -681,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>0</v>
@@ -695,7 +710,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>16734</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -716,14 +731,14 @@
         <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>16734</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>4:38:54</t>
         </is>
       </c>
     </row>
@@ -734,7 +749,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -755,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>0</v>
@@ -769,7 +784,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>10835</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -790,14 +805,14 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>10835</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>3:00:35</t>
         </is>
       </c>
     </row>
@@ -808,7 +823,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -829,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>0</v>
@@ -843,7 +858,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>27569</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -864,14 +879,14 @@
         <v>0</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0</v>
+        <v>27569</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>7:39:29</t>
         </is>
       </c>
     </row>
@@ -882,7 +897,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -903,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>0</v>
@@ -913,18 +928,18 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>10월 누적  (0일 / 1일 중 작업일)</t>
+          <t>10월 누적  (1일 / 1일 중 작업일)</t>
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>0</v>
+        <v>27569</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -947,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1034,91 +1049,783 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>985</v>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>0:16:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>R0.2_라핑</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>블루</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>198</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>0:03:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>R0.3</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>블루</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>356</v>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>0:05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>0:02:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>283</v>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>0:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>블루</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>0106 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>3679</v>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>1:01:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>블루</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>1415</v>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>0:23:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>0160</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>840</v>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>0:14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>2212</v>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>0:36:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>6636</v>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>1:50:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>FAST GRIND 소계</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>16734</v>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>4:38:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr"/>
+      <c r="I18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>454</v>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>0:07:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>354</v>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>0:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr"/>
+      <c r="I20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>177</v>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>0:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr"/>
+      <c r="I21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <v>177</v>
+      </c>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>0:02:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>0068 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr"/>
+      <c r="I22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>253</v>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>0:04:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr"/>
+      <c r="I23" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="24" t="n">
+        <v>9420</v>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>2:37:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>GX7 소계</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>10835</v>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>3:00:35</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
